--- a/bots/MAGALU/links_afiliados_magalu.xlsx
+++ b/bots/MAGALU/links_afiliados_magalu.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G64"/>
+  <dimension ref="A1:G68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2367,6 +2367,146 @@
         </is>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>banheiro</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/banheira-de-bebe-kiddo-maresias-cinza/p/238454600/bb/ifba/</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/jdxxfv03</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:27:04</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>banheiro</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>2</v>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/banheira-para-bebe-dobravel-portatil-2-em-1-com-assento-45l-cinza-pipdip/p/da8ecg07f2/bb/ifba/</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/te9ujmts</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:27:13</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>banheiro</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/cadeira-de-banho-higienica-d30-resistente-e-pratica-para-idoso-dellamed/p/ajd14134dh/cp/cbob/</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/w29xl1sf</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:27:35</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>banheiro</t>
+        </is>
+      </c>
+      <c r="B68" t="n">
+        <v>4</v>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/banheira-de-bebe-com-suporte-dobravel-maxi-baby-wish-branca-40l/p/240688100/bb/ifba/</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/th23l0l6</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:27:44</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bots/MAGALU/links_afiliados_magalu.xlsx
+++ b/bots/MAGALU/links_afiliados_magalu.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G68"/>
+  <dimension ref="A1:G89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -2507,6 +2507,726 @@
         </is>
       </c>
     </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/modelador-de-hamburguer-maquina-industrial-2-discos-lcg-eletro/p/df0h9410f6/ud/mdlh/</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/8qmggcu9</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:53:25</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B70" t="n">
+        <v>2</v>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/prensa-molde-para-hamburguer-carne-forma-de-hamburguer-generico/p/fgf70adgd2/am/mods/</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/4c2nxx2r</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:53:36</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B71" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/modelador-de-hamburguer-artesanal-prensa-aluminio-bazar-do-saara/p/kc7ffb0a59/ud/mdlh/</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/wpn8cgvz</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:53:45</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B72" t="n">
+        <v>4</v>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/forma-modeladora-para-fazer-molde-hamburguer-manual-recheado-plasutil/p/dk3135jg43/ud/mdlh/</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/wgdd686u</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:53:53</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B73" t="n">
+        <v>5</v>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/modelador-de-hamburguer-artesanal-aro-12cm-aluminio-redar/p/hj65k8b861/ud/comp/</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/rbth70os</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:54:00</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>hamburguer</t>
+        </is>
+      </c>
+      <c r="B74" t="n">
+        <v>6</v>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/forma-modelador-de-hamburguer-artesanal-caseiro-molde-para-hamburguer-gourmet-utensilios-cozinha-h-m/p/fj7ka0c476/ud/mdlh/</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:54:23</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Não foi possível obter o link de afiliado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-de-mesa-britania-1500w-de-potencia-bcq10a/p/240305900/fj/celt/</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/uj7jfxlp</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:54:45</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B76" t="n">
+        <v>2</v>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-portatil-2000w-mondial-grand-steak-e-grill-ch-05/p/236675000/fj/chua/</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:55:06</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Não foi possível obter o link de afiliado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B77" t="n">
+        <v>3</v>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-carvao-movel-california-preta-grelha-e-espetos-mor/p/ghd2j611ej/fj/chcv/</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/zlarvyj6</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:55:15</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B78" t="n">
+        <v>4</v>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-a-bafo-pequena-com-alta-eficiencia-no-preparo-de-carnes-e-grelhados-star-produtos/p/jh5a5g7df2/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/j2x80d6f</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:55:24</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B79" t="n">
+        <v>5</v>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-britania-1500w-bcq40/p/238193400/fj/chua/</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>REVISAR</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:55:47</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Não foi possível obter o link de afiliado.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B80" t="n">
+        <v>6</v>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-montana-mor-03005/p/jaf13a1j94/fj/chcv/</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/z2gp44ib</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:55:57</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B81" t="n">
+        <v>7</v>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-movel-com-tampa-bafinho-45x35x32cm-tambor-mini-preta-hn/p/ef3hhk049f/fj/chcv/</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/ugpdkpdz</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:06</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B82" t="n">
+        <v>8</v>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-portatil-apartamento-sem-fumaca-grill-2000w-grande-linha-premium-bak/p/dj6bfhj8h1/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/ic7er56s</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:13</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>9</v>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-portatil-apartamento-sem-fumaca-grill-2000w-grande-linha-premium-home-imports/p/hgfgfaj2c6/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/k58sfrsa</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:22</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B84" t="n">
+        <v>10</v>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-grill-galvanizada-c-grelha-portatil-aco-anti-corte-kvell/p/kb9b8cjf14/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/zt0ys40x</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:31</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B85" t="n">
+        <v>11</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-2000w-para-churrasco-110v-compacta-com-termostato-grelha-ajustavel-nza/p/af6f8k966k/fj/celt/</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/8s1kxj7b</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:40</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>12</v>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-movel-portatil-a-carvao-com-rodinhas-pro-tork-preto-grill-machine/p/gc009f997g/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/vbp51077</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:49</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>13</v>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-portatil-2000w-mondial-grand-steak-e-grill-ii-ch-06/p/236675200/fj/chua/</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/dz11rmkn</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:56:57</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>14</v>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-110v-1500w-sem-fumaca-grelhador-de-mesa-portatil-churrasco-cozinha-5-nivel-bak/p/edj950jjac/fj/jdim/</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/baalaqbc</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:57:05</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>churrasqueira</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>15</v>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-mondial-pratic-steak-gril-ch-07/p/237288100/fj/celt/</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/r9fv1z1n</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>12/08/2026 13:57:18</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/bots/MAGALU/links_afiliados_magalu.xlsx
+++ b/bots/MAGALU/links_afiliados_magalu.xlsx
@@ -413,16 +413,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G89"/>
+  <dimension ref="A1:I110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="80" customWidth="1" min="3" max="3"/>
     <col width="80" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="80" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="18" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
+    <col width="80" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -448,15 +450,25 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Preço Anterior</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Preço Atual</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Data/Hora</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Detalhes</t>
         </is>
@@ -881,21 +893,6 @@
           <t>https://magazineluiza.onelink.me/589508454/7aqau9u2</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:39:28</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -916,21 +913,6 @@
           <t>https://magazineluiza.onelink.me/589508454/z3tavd2r</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:39:38</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -951,21 +933,6 @@
           <t>https://magazineluiza.onelink.me/589508454/oj4pccpo</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:39:48</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -986,21 +953,6 @@
           <t>https://magazineluiza.onelink.me/589508454/b5e9he7b</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:39:57</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1021,21 +973,6 @@
           <t>https://magazineluiza.onelink.me/589508454/jlyx0mce</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:05</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1056,21 +993,6 @@
           <t>https://magazineluiza.onelink.me/589508454/1nmnlp33</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1091,21 +1013,6 @@
           <t>https://magazineluiza.onelink.me/589508454/pgmvtqet</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:23</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1126,21 +1033,6 @@
           <t>https://magazineluiza.onelink.me/589508454/skpsturj</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:32</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1161,21 +1053,6 @@
           <t>https://magazineluiza.onelink.me/589508454/90351uy7</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:42</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1196,21 +1073,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ftjukp6x</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:40:52</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1231,21 +1093,6 @@
           <t>https://magazineluiza.onelink.me/589508454/yfeizb7u</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:41:01</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1266,21 +1113,6 @@
           <t>https://magazineluiza.onelink.me/589508454/a12u4klp</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:41:09</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1301,21 +1133,6 @@
           <t>https://magazineluiza.onelink.me/589508454/reqi72k5</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:41:19</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1336,21 +1153,6 @@
           <t>https://magazineluiza.onelink.me/589508454/3gd2mwtg</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>12/08/2026 11:41:29</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1371,21 +1173,6 @@
           <t>https://magazineluiza.onelink.me/589508454/sy6upmmp</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:19:07</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1406,21 +1193,6 @@
           <t>https://magazineluiza.onelink.me/589508454/mo72c6d4</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:19:15</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1441,21 +1213,6 @@
           <t>https://magazineluiza.onelink.me/589508454/6012xkec</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:19:24</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1476,21 +1233,6 @@
           <t>https://magazineluiza.onelink.me/589508454/6zzx3gbb</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:27:36</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1511,21 +1253,6 @@
           <t>https://magazineluiza.onelink.me/589508454/uxxi6dwf</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:27:44</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1546,21 +1273,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ebfduu9o</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:27:53</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1581,21 +1293,6 @@
           <t>https://magazineluiza.onelink.me/589508454/raksvvbz</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:28:52</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1616,21 +1313,6 @@
           <t>https://magazineluiza.onelink.me/589508454/dt2h7w9f</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:29:04</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1651,21 +1333,6 @@
           <t>https://magazineluiza.onelink.me/589508454/23jdzuj7</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:29:14</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -1686,21 +1353,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ezlg9hpc</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:29:25</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -1721,21 +1373,6 @@
           <t>https://magazineluiza.onelink.me/589508454/6bcsb4p3</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:35:49</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -1756,21 +1393,6 @@
           <t>https://magazineluiza.onelink.me/589508454/2n2dky6s</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:35:59</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -1791,21 +1413,6 @@
           <t>https://magazineluiza.onelink.me/589508454/sw1skk9x</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:36:08</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -1826,21 +1433,6 @@
           <t>https://magazineluiza.onelink.me/589508454/fqey647r</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:36:18</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -1861,21 +1453,6 @@
           <t>https://magazineluiza.onelink.me/589508454/i7gho5cb</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:36:28</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -1896,21 +1473,6 @@
           <t>https://magazineluiza.onelink.me/589508454/75ele9ft</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:53:20</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -1931,21 +1493,6 @@
           <t>https://magazineluiza.onelink.me/589508454/isl142lk</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:53:29</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -1966,21 +1513,6 @@
           <t>https://magazineluiza.onelink.me/589508454/eqktymtl</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:53:39</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2001,21 +1533,6 @@
           <t>https://magazineluiza.onelink.me/589508454/1ce8wh9y</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:53:48</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2036,21 +1553,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ocigfxzk</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:53:58</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2071,21 +1573,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ei3dwam9</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:54:08</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2106,21 +1593,6 @@
           <t>https://magazineluiza.onelink.me/589508454/x8cfoofu</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F57" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:54:17</t>
-        </is>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2141,21 +1613,6 @@
           <t>https://magazineluiza.onelink.me/589508454/xwqfa7yh</t>
         </is>
       </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:54:26</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2176,21 +1633,6 @@
           <t>https://magazineluiza.onelink.me/589508454/2hswgum4</t>
         </is>
       </c>
-      <c r="E59" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:58:56</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2211,21 +1653,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ol437zvo</t>
         </is>
       </c>
-      <c r="E60" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:59:04</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2246,21 +1673,6 @@
           <t>https://magazineluiza.onelink.me/589508454/uixw6072</t>
         </is>
       </c>
-      <c r="E61" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F61" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:59:13</t>
-        </is>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2281,21 +1693,6 @@
           <t>https://magazineluiza.onelink.me/589508454/kzxb6a0n</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F62" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:59:22</t>
-        </is>
-      </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2316,21 +1713,6 @@
           <t>https://magazineluiza.onelink.me/589508454/5xmsocxm</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:59:30</t>
-        </is>
-      </c>
-      <c r="G63" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2351,21 +1733,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ewwupz4m</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>12/08/2026 12:59:39</t>
-        </is>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2386,21 +1753,6 @@
           <t>https://magazineluiza.onelink.me/589508454/jdxxfv03</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:27:04</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2421,21 +1773,6 @@
           <t>https://magazineluiza.onelink.me/589508454/te9ujmts</t>
         </is>
       </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:27:13</t>
-        </is>
-      </c>
-      <c r="G66" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2456,21 +1793,6 @@
           <t>https://magazineluiza.onelink.me/589508454/w29xl1sf</t>
         </is>
       </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:27:35</t>
-        </is>
-      </c>
-      <c r="G67" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2491,21 +1813,6 @@
           <t>https://magazineluiza.onelink.me/589508454/th23l0l6</t>
         </is>
       </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:27:44</t>
-        </is>
-      </c>
-      <c r="G68" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2526,21 +1833,6 @@
           <t>https://magazineluiza.onelink.me/589508454/8qmggcu9</t>
         </is>
       </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:53:25</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2561,21 +1853,6 @@
           <t>https://magazineluiza.onelink.me/589508454/4c2nxx2r</t>
         </is>
       </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:53:36</t>
-        </is>
-      </c>
-      <c r="G70" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2596,21 +1873,6 @@
           <t>https://magazineluiza.onelink.me/589508454/wpn8cgvz</t>
         </is>
       </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F71" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:53:45</t>
-        </is>
-      </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -2631,21 +1893,6 @@
           <t>https://magazineluiza.onelink.me/589508454/wgdd686u</t>
         </is>
       </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:53:53</t>
-        </is>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -2666,21 +1913,6 @@
           <t>https://magazineluiza.onelink.me/589508454/rbth70os</t>
         </is>
       </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:54:00</t>
-        </is>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -2696,21 +1928,6 @@
           <t>https://www.magazinevoce.com.br/magazineblackriseco/forma-modelador-de-hamburguer-artesanal-caseiro-molde-para-hamburguer-gourmet-utensilios-cozinha-h-m/p/fj7ka0c476/ud/mdlh/</t>
         </is>
       </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:54:23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>Não foi possível obter o link de afiliado.</t>
-        </is>
-      </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -2731,21 +1948,6 @@
           <t>https://magazineluiza.onelink.me/589508454/uj7jfxlp</t>
         </is>
       </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:54:45</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -2761,21 +1963,6 @@
           <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-portatil-2000w-mondial-grand-steak-e-grill-ch-05/p/236675000/fj/chua/</t>
         </is>
       </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:55:06</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Não foi possível obter o link de afiliado.</t>
-        </is>
-      </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -2796,21 +1983,6 @@
           <t>https://magazineluiza.onelink.me/589508454/zlarvyj6</t>
         </is>
       </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:55:15</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -2831,21 +2003,6 @@
           <t>https://magazineluiza.onelink.me/589508454/j2x80d6f</t>
         </is>
       </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:55:24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -2861,21 +2018,6 @@
           <t>https://www.magazinevoce.com.br/magazineblackriseco/churrasqueira-eletrica-britania-1500w-bcq40/p/238193400/fj/chua/</t>
         </is>
       </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>REVISAR</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:55:47</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>Não foi possível obter o link de afiliado.</t>
-        </is>
-      </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -2896,21 +2038,6 @@
           <t>https://magazineluiza.onelink.me/589508454/z2gp44ib</t>
         </is>
       </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:55:57</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -2931,21 +2058,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ugpdkpdz</t>
         </is>
       </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:06</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -2966,21 +2078,6 @@
           <t>https://magazineluiza.onelink.me/589508454/ic7er56s</t>
         </is>
       </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:13</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3001,21 +2098,6 @@
           <t>https://magazineluiza.onelink.me/589508454/k58sfrsa</t>
         </is>
       </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:22</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3036,21 +2118,6 @@
           <t>https://magazineluiza.onelink.me/589508454/zt0ys40x</t>
         </is>
       </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:31</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3071,21 +2138,6 @@
           <t>https://magazineluiza.onelink.me/589508454/8s1kxj7b</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:40</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3106,21 +2158,6 @@
           <t>https://magazineluiza.onelink.me/589508454/vbp51077</t>
         </is>
       </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:49</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3141,21 +2178,6 @@
           <t>https://magazineluiza.onelink.me/589508454/dz11rmkn</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:56:57</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3176,21 +2198,6 @@
           <t>https://magazineluiza.onelink.me/589508454/baalaqbc</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>OK</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:57:05</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>Link de afiliado obtido com sucesso.</t>
-        </is>
-      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3211,17 +2218,582 @@
           <t>https://magazineluiza.onelink.me/589508454/r9fv1z1n</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-turim-para-tv-ate-65-polegadas-com-pes-madeira-moveis-bechara/p/bd54f5g74k/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/fxc1sisc</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>2</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-sala-tv-ate-75-polegadas-2-portas-1-gaveta-reims-madesa/p/gjh61f407b/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/hdhpy2gg</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B92" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-bancada-sala-de-estar-para-tv-50-55-60-70-polegadas-sevilla-movelove-2-portas-1-gaveta-lukaliam-moveis/p/dkd57akc0d/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/u9rowa9o</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B93" t="n">
+        <v>4</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-rubi-1-2-para-tv-ate-50-2-portas-pe-madeira-macica-moveis-bechara/p/feb36akh4g/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/2d5iwwos</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>5</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-estar-tv-55-polegadas-madeira-white-organizador-deltre/p/bejf052e58/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/rtf57vou</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>6</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-prateleira-bancada-sala-tv-90-cm-pe-retro-regulaveis-digo-casa/p/da31jaj2j7/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/4392b3ht</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B96" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-home-classic-decoracao-casa-apartamento-pequeno-sala-estar-quarto-tv-32-polegadas-2-portas-lojas-comprou-chegou/p/bhf9h539g9/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/9s07248p</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B97" t="n">
+        <v>8</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-com-2-prateleiras-para-tv-ate-50-branco-deltre/p/adfaa5c998/mo/rkcp/</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/9986zbrp</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>quarto</t>
+        </is>
+      </c>
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/quarto-infantil-com-guarda-roupa-4-portas-e-comoda-1-porta-100-mdf-mimo-espresso-moveis-branco-brilho-amendoa/p/jh7774jf5a/mo/qtic/</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/e4a4x7ie</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>quarto</t>
+        </is>
+      </c>
+      <c r="B99" t="n">
+        <v>2</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-multiuso-clean-4-portas-6-nichos-organizador-lavanderia-quarto-cozinha-envio-imediato-dullar-moveis/p/be2k294j3c/mo/momu/</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/4s5munnu</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-sala-estar-malbec-wood-tv-ate-55-giga-moveis/p/kkf5ac5f1g/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/koq0pt1a</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>2</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-sala-tv-ate-65-polegadas-com-pes-dubai-madesa-02/p/gf5f1kdgb6/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/03p1r468</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>R$ 409,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B102" t="n">
+        <v>3</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-miami-home-theater-tv-ate-55-polegadas-125-cm-1-porta-1-prateleira-sala-de-estar-preto-j-carvalho/p/dkee8eg57c/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/2hob2msb</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>R$ 289,90</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B103" t="n">
+        <v>4</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-tv-ate-55-polegadas-para-sala-home-multiuso-white-demoveis/p/ak2hggfg89/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/gioogwfb</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>R$ 347,89</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B104" t="n">
+        <v>5</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-tvs-ate-43-polegadas-pes-palito-retro-sala-quarto-1-porta-bancada-eder-cores-mjm-casa-dos-moveis/p/fjc932acj4/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/uz3zqc2f</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-compacta-demobile-select-com-balcao-nicho-para-micro-ondas-6-portas-2-gavetas/p/234470600/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/ll40r5su</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>R$ 1.099,00</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>ou R$ 759,99</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
         <is>
           <t>OK</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>12/08/2026 13:57:18</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:10:07</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B106" t="n">
+        <v>2</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-compacto-8-portas-2-gavetass-com-nicho-vogue-kits-parana/p/jhfe09bh6k/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/79touoon</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>R$ 615,88</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>ou R$ 416,42</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:10:21</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B107" t="n">
+        <v>3</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-compacta-itatiaia-amanda-aco-com-balcao-10-portas-1-gaveta/p/237989500/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/a7ocaoqn</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>R$ 1.199,00</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>ou R$ 989,99</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:10:31</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B108" t="n">
+        <v>4</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-compacta-196cm-aura-madesa/p/bba6734eeh/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/g1cvkg51</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>R$ 799,99</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>ou R$ 577,99</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:10:41</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B109" t="n">
+        <v>5</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-compacta-sofia-multimoveis-preta/p/cj42317a5a/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/arjf9myd</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>ou R$ 494,99</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:10:59</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>cozinha</t>
+        </is>
+      </c>
+      <c r="B110" t="n">
+        <v>6</v>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/armario-de-cozinha-aereo-itatiaia-rose-arm-105-3-portas-105x40cm/p/237989400/mo/moac/</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/ckptlush</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>R$ 300,00</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>ou R$ 242,99</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>13/08/2026 12:11:11</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
         <is>
           <t>Link de afiliado obtido com sucesso.</t>
         </is>

--- a/bots/MAGALU/links_afiliados_magalu.xlsx
+++ b/bots/MAGALU/links_afiliados_magalu.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I1"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
@@ -474,6 +474,381 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>quarto</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/guarda-roupa-de-casal-6-portas-e-guarda-roupa-de-casal-lite-6-portas-para-quarto-grande-com-cabideiro-prateleiras-e-gavetas-cor-off-white-e-2-gavetas-maxi-do-brasil/p/ej891ba89k/mo/guro/</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>R$ 899,90</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>quarto</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/quarto-de-bebe-completo-com-berco-comoda-e-guarda-roupa-henn-ternura-branco-e-jequitiba/p/238472900/mo/qdbc/</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>R$ 2.849,90</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-turim-para-tv-ate-65-polegadas-com-pes-madeira-moveis-bechara/p/bd54f5g74k/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/7r5wyofp</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ou R$ 367,83</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:02:32</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-rubi-1-2-para-tv-ate-50-2-portas-pe-madeira-macica-moveis-bechara/p/feb36akh4g/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/l83rpea8</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>ou R$ 316,00</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:02:47</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-sala-tv-ate-75-polegadas-2-portas-1-gaveta-reims-madesa/p/gjh61f407b/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/cqswnra3</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>R$ 549,99</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>ou R$ 431,99</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:02:58</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>4</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-florenca-para-tv-ate-70-polegadas-com-pes-madeira-moveis-bechara/p/ghge305f23/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/m2oxm9xr</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>ou R$ 459,79</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:03:14</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>5</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-bancada-sala-de-estar-para-tv-50-55-60-70-polegadas-sevilla-movelove-2-portas-1-gaveta-lukaliam-moveis/p/dkd57akc0d/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/evry4ftu</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ou R$ 478,63</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:03:31</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>6</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-sala-estar-tv-55-polegadas-madeira-white-organizador-deltre/p/bejf052e58/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/uo7gslz7</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>R$ 424,05</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>ou R$ 352,74</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:03:44</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>7</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-para-sala-estar-malbec-wood-tv-ate-55-giga-moveis/p/kkf5ac5f1g/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/ewlj7a7c</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>ou R$ 284,99</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:04:00</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>sala</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>8</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>https://www.magazinevoce.com.br/magazineblackriseco/rack-home-classic-decoracao-casa-apartamento-pequeno-sala-estar-quarto-tv-32-polegadas-2-portas-lojas-comprou-chegou/p/bhf9h539g9/mo/racm/</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>https://magazineluiza.onelink.me/589508454/r2pefg97</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>R$ 299,90</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>ou R$ 218,37</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>19/08/2026 23:04:12</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>Link de afiliado obtido com sucesso.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
